--- a/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02E8FFA-8F89-4B65-80B7-C5E8846518A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1522A562-3D55-43DA-B609-42C1B802CAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18990,8 +18990,8 @@
       <c r="D257">
         <v>34</v>
       </c>
-      <c r="E257">
-        <v>65535</v>
+      <c r="E257" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F257">
         <v>2.42</v>
@@ -18999,8 +18999,8 @@
       <c r="H257">
         <v>1.18</v>
       </c>
-      <c r="I257">
-        <v>65535</v>
+      <c r="I257" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J257">
         <v>2.0099999999999998</v>
@@ -19028,8 +19028,8 @@
       <c r="D258">
         <v>34</v>
       </c>
-      <c r="E258">
-        <v>65535</v>
+      <c r="E258" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F258">
         <v>3.1</v>
@@ -19037,8 +19037,8 @@
       <c r="H258">
         <v>1.71</v>
       </c>
-      <c r="I258">
-        <v>65535</v>
+      <c r="I258" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J258">
         <v>2.38</v>
@@ -19066,8 +19066,8 @@
       <c r="D259">
         <v>34</v>
       </c>
-      <c r="E259">
-        <v>65535</v>
+      <c r="E259" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F259">
         <v>3.54</v>
@@ -19075,8 +19075,8 @@
       <c r="H259">
         <v>1.91</v>
       </c>
-      <c r="I259">
-        <v>65535</v>
+      <c r="I259" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J259">
         <v>2.66</v>
@@ -19104,8 +19104,8 @@
       <c r="D260">
         <v>34</v>
       </c>
-      <c r="E260">
-        <v>65535</v>
+      <c r="E260" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F260">
         <v>4.0999999999999996</v>
@@ -19113,8 +19113,8 @@
       <c r="H260">
         <v>2.27</v>
       </c>
-      <c r="I260">
-        <v>65535</v>
+      <c r="I260" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J260">
         <v>2.96</v>
@@ -19142,8 +19142,8 @@
       <c r="D261">
         <v>34</v>
       </c>
-      <c r="E261">
-        <v>65535</v>
+      <c r="E261" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F261">
         <v>3.86</v>
@@ -19151,8 +19151,8 @@
       <c r="H261">
         <v>2.54</v>
       </c>
-      <c r="I261">
-        <v>65535</v>
+      <c r="I261" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J261">
         <v>3.3</v>
@@ -19180,8 +19180,8 @@
       <c r="D262">
         <v>34</v>
       </c>
-      <c r="E262">
-        <v>65535</v>
+      <c r="E262" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F262">
         <v>3.59</v>
@@ -19189,8 +19189,8 @@
       <c r="H262">
         <v>2.73</v>
       </c>
-      <c r="I262">
-        <v>65535</v>
+      <c r="I262" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J262">
         <v>3.07</v>
@@ -19259,8 +19259,8 @@
       <c r="D264">
         <v>44</v>
       </c>
-      <c r="E264">
-        <v>65535</v>
+      <c r="E264" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F264">
         <v>1.22</v>
@@ -19268,8 +19268,8 @@
       <c r="H264">
         <v>0</v>
       </c>
-      <c r="I264">
-        <v>65535</v>
+      <c r="I264" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J264">
         <v>1.1299999999999999</v>
@@ -19297,8 +19297,8 @@
       <c r="D265">
         <v>44</v>
       </c>
-      <c r="E265">
-        <v>65535</v>
+      <c r="E265" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F265">
         <v>1.5</v>
@@ -19306,8 +19306,8 @@
       <c r="H265">
         <v>0</v>
       </c>
-      <c r="I265">
-        <v>65535</v>
+      <c r="I265" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J265">
         <v>1.31</v>
@@ -19335,8 +19335,8 @@
       <c r="D266">
         <v>44</v>
       </c>
-      <c r="E266">
-        <v>65535</v>
+      <c r="E266" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F266">
         <v>2.12</v>
@@ -19344,8 +19344,8 @@
       <c r="H266">
         <v>0</v>
       </c>
-      <c r="I266">
-        <v>65535</v>
+      <c r="I266" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J266">
         <v>1.68</v>
@@ -19373,8 +19373,8 @@
       <c r="D267">
         <v>44</v>
       </c>
-      <c r="E267">
-        <v>65535</v>
+      <c r="E267" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F267">
         <v>2.5</v>
@@ -19382,8 +19382,8 @@
       <c r="H267">
         <v>0</v>
       </c>
-      <c r="I267">
-        <v>65535</v>
+      <c r="I267" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J267">
         <v>2</v>
@@ -19411,8 +19411,8 @@
       <c r="D268">
         <v>44</v>
       </c>
-      <c r="E268">
-        <v>65535</v>
+      <c r="E268" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F268">
         <v>2.79</v>
@@ -19420,8 +19420,8 @@
       <c r="H268">
         <v>0</v>
       </c>
-      <c r="I268">
-        <v>65535</v>
+      <c r="I268" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J268">
         <v>2.08</v>
@@ -19449,8 +19449,8 @@
       <c r="D269">
         <v>44</v>
       </c>
-      <c r="E269">
-        <v>65535</v>
+      <c r="E269" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F269">
         <v>2.95</v>
@@ -19458,8 +19458,8 @@
       <c r="H269">
         <v>0</v>
       </c>
-      <c r="I269">
-        <v>65535</v>
+      <c r="I269" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J269">
         <v>2.4900000000000002</v>
@@ -19528,8 +19528,8 @@
       <c r="D271">
         <v>112</v>
       </c>
-      <c r="E271">
-        <v>65535</v>
+      <c r="E271" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F271">
         <v>1.41</v>
@@ -19537,8 +19537,8 @@
       <c r="H271">
         <v>0.98</v>
       </c>
-      <c r="I271">
-        <v>65535</v>
+      <c r="I271" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J271">
         <v>1.23</v>
@@ -19566,8 +19566,8 @@
       <c r="D272">
         <v>112</v>
       </c>
-      <c r="E272">
-        <v>65535</v>
+      <c r="E272" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F272">
         <v>2.04</v>
@@ -19575,8 +19575,8 @@
       <c r="H272">
         <v>1.05</v>
       </c>
-      <c r="I272">
-        <v>65535</v>
+      <c r="I272" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J272">
         <v>1.52</v>
@@ -19604,8 +19604,8 @@
       <c r="D273">
         <v>112</v>
       </c>
-      <c r="E273">
-        <v>65535</v>
+      <c r="E273" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F273">
         <v>2.4</v>
@@ -19613,8 +19613,8 @@
       <c r="H273">
         <v>1.05</v>
       </c>
-      <c r="I273">
-        <v>65535</v>
+      <c r="I273" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J273">
         <v>1.71</v>
@@ -19642,8 +19642,8 @@
       <c r="D274">
         <v>112</v>
       </c>
-      <c r="E274">
-        <v>65535</v>
+      <c r="E274" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F274">
         <v>2.6</v>
@@ -19651,8 +19651,8 @@
       <c r="H274">
         <v>1.06</v>
       </c>
-      <c r="I274">
-        <v>65535</v>
+      <c r="I274" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J274">
         <v>1.85</v>
@@ -19680,8 +19680,8 @@
       <c r="D275">
         <v>112</v>
       </c>
-      <c r="E275">
-        <v>65535</v>
+      <c r="E275" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F275">
         <v>2.85</v>
@@ -19689,8 +19689,8 @@
       <c r="H275">
         <v>1.08</v>
       </c>
-      <c r="I275">
-        <v>65535</v>
+      <c r="I275" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J275">
         <v>2</v>
@@ -19718,8 +19718,8 @@
       <c r="D276">
         <v>112</v>
       </c>
-      <c r="E276">
-        <v>65535</v>
+      <c r="E276" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F276">
         <v>2.97</v>
@@ -19727,8 +19727,8 @@
       <c r="H276">
         <v>0</v>
       </c>
-      <c r="I276">
-        <v>65535</v>
+      <c r="I276" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J276">
         <v>2.15</v>
@@ -20371,8 +20371,8 @@
       <c r="D292">
         <v>50</v>
       </c>
-      <c r="E292">
-        <v>65535</v>
+      <c r="E292" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F292">
         <v>1.1000000000000001</v>
@@ -20380,8 +20380,8 @@
       <c r="H292">
         <v>-4.33</v>
       </c>
-      <c r="I292">
-        <v>65535</v>
+      <c r="I292" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J292">
         <v>0.81</v>
@@ -20409,8 +20409,8 @@
       <c r="D293">
         <v>50</v>
       </c>
-      <c r="E293">
-        <v>65535</v>
+      <c r="E293" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F293">
         <v>1.77</v>
@@ -20418,8 +20418,8 @@
       <c r="H293">
         <v>-6.1</v>
       </c>
-      <c r="I293">
-        <v>65535</v>
+      <c r="I293" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J293">
         <v>1.27</v>
@@ -20447,8 +20447,8 @@
       <c r="D294">
         <v>50</v>
       </c>
-      <c r="E294">
-        <v>65535</v>
+      <c r="E294" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F294">
         <v>1.87</v>
@@ -20456,8 +20456,8 @@
       <c r="H294">
         <v>-6.86</v>
       </c>
-      <c r="I294">
-        <v>65535</v>
+      <c r="I294" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J294">
         <v>1.1499999999999999</v>
@@ -20485,8 +20485,8 @@
       <c r="D295">
         <v>50</v>
       </c>
-      <c r="E295">
-        <v>65535</v>
+      <c r="E295" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F295">
         <v>1.96</v>
@@ -20494,8 +20494,8 @@
       <c r="H295">
         <v>-9.2100000000000009</v>
       </c>
-      <c r="I295">
-        <v>65535</v>
+      <c r="I295" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J295">
         <v>1.31</v>
@@ -20523,8 +20523,8 @@
       <c r="D296">
         <v>50</v>
       </c>
-      <c r="E296">
-        <v>65535</v>
+      <c r="E296" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F296">
         <v>2.13</v>
@@ -20532,8 +20532,8 @@
       <c r="H296">
         <v>-6.95</v>
       </c>
-      <c r="I296">
-        <v>65535</v>
+      <c r="I296" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J296">
         <v>1.6</v>
@@ -20561,8 +20561,8 @@
       <c r="D297">
         <v>50</v>
       </c>
-      <c r="E297">
-        <v>65535</v>
+      <c r="E297" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F297">
         <v>2</v>
@@ -20570,8 +20570,8 @@
       <c r="H297">
         <v>-10.07</v>
       </c>
-      <c r="I297">
-        <v>65535</v>
+      <c r="I297" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J297">
         <v>1.55</v>
@@ -20640,8 +20640,8 @@
       <c r="D299">
         <v>52</v>
       </c>
-      <c r="E299">
-        <v>65535</v>
+      <c r="E299" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F299">
         <v>0.61</v>
@@ -20649,8 +20649,8 @@
       <c r="H299">
         <v>0</v>
       </c>
-      <c r="I299">
-        <v>65535</v>
+      <c r="I299" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J299">
         <v>0.53</v>
@@ -20678,8 +20678,8 @@
       <c r="D300">
         <v>63</v>
       </c>
-      <c r="E300">
-        <v>65535</v>
+      <c r="E300" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F300">
         <v>1.07</v>
@@ -20687,8 +20687,8 @@
       <c r="H300">
         <v>0</v>
       </c>
-      <c r="I300">
-        <v>65535</v>
+      <c r="I300" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J300">
         <v>0.6</v>
@@ -20716,8 +20716,8 @@
       <c r="D301">
         <v>52</v>
       </c>
-      <c r="E301">
-        <v>65535</v>
+      <c r="E301" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F301">
         <v>1.0900000000000001</v>
@@ -20725,8 +20725,8 @@
       <c r="H301">
         <v>0</v>
       </c>
-      <c r="I301">
-        <v>65535</v>
+      <c r="I301" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J301">
         <v>0.6</v>
@@ -20754,8 +20754,8 @@
       <c r="D302">
         <v>63</v>
       </c>
-      <c r="E302">
-        <v>65535</v>
+      <c r="E302" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F302">
         <v>1.25</v>
@@ -20763,8 +20763,8 @@
       <c r="H302">
         <v>0</v>
       </c>
-      <c r="I302">
-        <v>65535</v>
+      <c r="I302" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J302">
         <v>0.87</v>
@@ -20792,8 +20792,8 @@
       <c r="D303">
         <v>52</v>
       </c>
-      <c r="E303">
-        <v>65535</v>
+      <c r="E303" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F303">
         <v>1.35</v>
@@ -20801,8 +20801,8 @@
       <c r="H303">
         <v>0</v>
       </c>
-      <c r="I303">
-        <v>65535</v>
+      <c r="I303" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J303">
         <v>0.78</v>
@@ -20830,8 +20830,8 @@
       <c r="D304">
         <v>63</v>
       </c>
-      <c r="E304">
-        <v>65535</v>
+      <c r="E304" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F304">
         <v>1.62</v>
@@ -20839,8 +20839,8 @@
       <c r="H304">
         <v>-2.31</v>
       </c>
-      <c r="I304">
-        <v>65535</v>
+      <c r="I304" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J304">
         <v>0.61</v>
@@ -20909,8 +20909,8 @@
       <c r="D306">
         <v>163</v>
       </c>
-      <c r="E306">
-        <v>65535</v>
+      <c r="E306" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F306">
         <v>0.75</v>
@@ -20918,8 +20918,8 @@
       <c r="H306">
         <v>0.46</v>
       </c>
-      <c r="I306">
-        <v>65535</v>
+      <c r="I306" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J306">
         <v>0.54</v>
@@ -20947,8 +20947,8 @@
       <c r="D307">
         <v>166</v>
       </c>
-      <c r="E307">
-        <v>65535</v>
+      <c r="E307" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F307">
         <v>1.1499999999999999</v>
@@ -20956,8 +20956,8 @@
       <c r="H307">
         <v>0.51</v>
       </c>
-      <c r="I307">
-        <v>65535</v>
+      <c r="I307" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J307">
         <v>0.74</v>
@@ -20985,8 +20985,8 @@
       <c r="D308">
         <v>163</v>
       </c>
-      <c r="E308">
-        <v>65535</v>
+      <c r="E308" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F308">
         <v>1.21</v>
@@ -20994,8 +20994,8 @@
       <c r="H308">
         <v>-0.95</v>
       </c>
-      <c r="I308">
-        <v>65535</v>
+      <c r="I308" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J308">
         <v>0.88</v>
@@ -21023,8 +21023,8 @@
       <c r="D309">
         <v>166</v>
       </c>
-      <c r="E309">
-        <v>65535</v>
+      <c r="E309" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F309">
         <v>1.28</v>
@@ -21032,8 +21032,8 @@
       <c r="H309">
         <v>-1.8</v>
       </c>
-      <c r="I309">
-        <v>65535</v>
+      <c r="I309" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J309">
         <v>0.89</v>
@@ -21061,8 +21061,8 @@
       <c r="D310">
         <v>163</v>
       </c>
-      <c r="E310">
-        <v>65535</v>
+      <c r="E310" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F310">
         <v>1.48</v>
@@ -21070,8 +21070,8 @@
       <c r="H310">
         <v>-5.93</v>
       </c>
-      <c r="I310">
-        <v>65535</v>
+      <c r="I310" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J310">
         <v>1.08</v>
@@ -21099,8 +21099,8 @@
       <c r="D311">
         <v>166</v>
       </c>
-      <c r="E311">
-        <v>65535</v>
+      <c r="E311" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F311">
         <v>1.59</v>
@@ -21108,8 +21108,8 @@
       <c r="H311">
         <v>-5.35</v>
       </c>
-      <c r="I311">
-        <v>65535</v>
+      <c r="I311" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J311">
         <v>0.97</v>
